--- a/PrepEdge-Users.xlsx
+++ b/PrepEdge-Users.xlsx
@@ -19,7 +19,7 @@
     <t>Comprehensive Registrant Engagement and Performance Summary</t>
   </si>
   <si>
-    <t>Report Generated: 06 April 2026  •  Sync Strength: 25 Active Records</t>
+    <t>Report Generated: 07 April 2026  •  Sync Strength: 25 Active Records</t>
   </si>
   <si>
     <t>INDEX</t>

--- a/PrepEdge-Users.xlsx
+++ b/PrepEdge-Users.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="93">
   <si>
     <t>PrepEdge — Official User Analytics &amp; Database Report</t>
   </si>
@@ -19,7 +19,7 @@
     <t>Comprehensive Registrant Engagement and Performance Summary</t>
   </si>
   <si>
-    <t>Report Generated: 07 April 2026  •  Sync Strength: 25 Active Records</t>
+    <t>Report Generated: 06 May 2026  •  Sync Strength: 29 Active Records</t>
   </si>
   <si>
     <t>INDEX</t>
@@ -121,6 +121,15 @@
     <t>kuldeep@gmial.com</t>
   </si>
   <si>
+    <t>Test User</t>
+  </si>
+  <si>
+    <t>testuser_antigravity_unique_123@example.com</t>
+  </si>
+  <si>
+    <t>11 Apr 2026, 05:14 pm</t>
+  </si>
+  <si>
     <t>Ajay Sharma</t>
   </si>
   <si>
@@ -196,6 +205,12 @@
     <t>24 Mar 2026, 09:57 pm</t>
   </si>
   <si>
+    <t>testuser_antigravity_unique_456@example.com</t>
+  </si>
+  <si>
+    <t>11 Apr 2026, 05:24 pm</t>
+  </si>
+  <si>
     <t xml:space="preserve">Raj Chouhan </t>
   </si>
   <si>
@@ -208,8 +223,9 @@
     <t>04 Apr 2026, 11:57 am</t>
   </si>
   <si>
-    <t xml:space="preserve">[5★] The PrepEdge website is well structure  and ease to understanding thier mock interiviw sysmtem . 
- | [5★] This website is very well structure and good.</t>
+    <t xml:space="preserve">[5★] good
+ | [5★] The PrepEdge website is well structure  and ease to understanding thier mock interiviw sysmtem . 
+ | [1★] not bad | [5★] This website is very well structure and good.</t>
   </si>
   <si>
     <t>iuh</t>
@@ -221,6 +237,12 @@
     <t>31 Mar 2026, 01:05 pm</t>
   </si>
   <si>
+    <t>testuser_antigravity@example.com</t>
+  </si>
+  <si>
+    <t>11 Apr 2026, 05:09 pm</t>
+  </si>
+  <si>
     <t>amit Shinde</t>
   </si>
   <si>
@@ -260,7 +282,16 @@
     <t>05 Apr 2026, 12:11 am</t>
   </si>
   <si>
-    <t>PREPEDGE PLATFORM INSIGHT • TOTAL USERS: 25 • SUCCESSFUL EXPORT</t>
+    <t>Amir  Sharma</t>
+  </si>
+  <si>
+    <t>amirsharma2020@gmail.com</t>
+  </si>
+  <si>
+    <t>07 Apr 2026, 10:33 pm</t>
+  </si>
+  <si>
+    <t>PREPEDGE PLATFORM INSIGHT • TOTAL USERS: 29 • SUCCESSFUL EXPORT</t>
   </si>
 </sst>
 </file>
@@ -776,7 +807,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr defaultRowHeight="24" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1005,7 +1036,7 @@
         <v>38</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1013,13 +1044,13 @@
         <v>11</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>15</v>
@@ -1030,7 +1061,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="C18" s="13" t="s">
         <v>42</v>
@@ -1056,7 +1087,7 @@
         <v>46</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1081,16 +1112,16 @@
         <v>15</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1098,7 +1129,7 @@
         <v>16</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="C22" s="13" t="s">
         <v>53</v>
@@ -1124,7 +1155,7 @@
         <v>57</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1141,7 +1172,7 @@
         <v>60</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1166,16 +1197,16 @@
         <v>20</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1200,16 +1231,16 @@
         <v>22</v>
       </c>
       <c r="B28" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="D28" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="C28" s="13" t="s">
+      <c r="E28" s="15" t="s">
         <v>70</v>
-      </c>
-      <c r="D28" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="E28" s="15" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="29" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1217,13 +1248,13 @@
         <v>23</v>
       </c>
       <c r="B29" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C29" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="D29" s="9" t="s">
         <v>73</v>
-      </c>
-      <c r="D29" s="9" t="s">
-        <v>74</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>15</v>
@@ -1234,16 +1265,16 @@
         <v>24</v>
       </c>
       <c r="B30" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="D30" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="D30" s="14" t="s">
-        <v>77</v>
-      </c>
       <c r="E30" s="15" t="s">
-        <v>78</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1251,33 +1282,101 @@
         <v>25</v>
       </c>
       <c r="B31" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E31" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="11">
+        <v>26</v>
+      </c>
+      <c r="B32" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="C31" s="8" t="s">
+      <c r="C32" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="D31" s="9" t="s">
+      <c r="D32" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="E31" s="10" t="s">
+      <c r="E32" s="15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="6">
+        <v>27</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="E33" s="10" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="11">
+        <v>28</v>
+      </c>
+      <c r="B34" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="D34" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="E34" s="15" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="33" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="16" t="s">
-        <v>82</v>
-      </c>
-      <c r="B33" s="16"/>
-      <c r="C33" s="16"/>
-      <c r="D33" s="16"/>
-      <c r="E33" s="16"/>
+    <row r="35" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="6">
+        <v>29</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="E35" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="37" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="B37" s="16"/>
+      <c r="C37" s="16"/>
+      <c r="D37" s="16"/>
+      <c r="E37" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A37:E37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
